--- a/AAII_Financials/Quarterly/IVDN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IVDN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>IVDN</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -793,31 +797,31 @@
         <v>100</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -826,10 +830,10 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -844,37 +848,40 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
       <c r="Z8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <v>100</v>
       </c>
       <c r="AB8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <v>200</v>
       </c>
       <c r="AE8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -882,7 +889,7 @@
         <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -891,10 +898,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -903,19 +910,19 @@
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
         <v>0</v>
@@ -933,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
@@ -942,28 +949,31 @@
         <v>100</v>
       </c>
       <c r="Y9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3">
         <v>100</v>
       </c>
       <c r="AB9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="3">
         <v>100</v>
       </c>
       <c r="AE9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -986,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -1001,13 +1011,13 @@
         <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Q10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
         <v>0</v>
@@ -1028,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="X10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z10" s="3">
         <v>0</v>
@@ -1043,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="AC10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="3">
         <v>100</v>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1288,11 +1308,11 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
@@ -1303,8 +1323,8 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1312,20 +1332,20 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
@@ -1336,8 +1356,8 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1351,16 +1371,19 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>4</v>
@@ -1377,8 +1400,8 @@
       <c r="J15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1496,9 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1479,26 +1506,26 @@
         <v>200</v>
       </c>
       <c r="E17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F17" s="3">
         <v>100</v>
       </c>
       <c r="G17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H17" s="3">
         <v>200</v>
       </c>
       <c r="I17" s="3">
+        <v>200</v>
+      </c>
+      <c r="J17" s="3">
         <v>300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
-        <v>100</v>
-      </c>
       <c r="L17" s="3">
         <v>100</v>
       </c>
@@ -1521,19 +1548,19 @@
         <v>100</v>
       </c>
       <c r="S17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U17" s="3">
         <v>200</v>
       </c>
       <c r="V17" s="3">
+        <v>200</v>
+      </c>
+      <c r="W17" s="3">
         <v>400</v>
-      </c>
-      <c r="W17" s="3">
-        <v>200</v>
       </c>
       <c r="X17" s="3">
         <v>200</v>
@@ -1542,25 +1569,28 @@
         <v>200</v>
       </c>
       <c r="Z17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA17" s="3">
         <v>300</v>
       </c>
       <c r="AB17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC17" s="3">
         <v>200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>500</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>300</v>
       </c>
       <c r="AE17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1571,28 +1601,28 @@
         <v>-100</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-100</v>
-      </c>
       <c r="I18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
-        <v>-100</v>
-      </c>
       <c r="K18" s="3">
         <v>-100</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
@@ -1601,31 +1631,31 @@
         <v>-100</v>
       </c>
       <c r="P18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R18" s="3">
         <v>-100</v>
       </c>
       <c r="S18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3">
         <v>-200</v>
       </c>
       <c r="V18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
-        <v>-100</v>
-      </c>
       <c r="X18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y18" s="3">
         <v>-200</v>
@@ -1640,16 +1670,19 @@
         <v>-200</v>
       </c>
       <c r="AC18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AD18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1696,14 +1730,14 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1717,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1735,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1770,13 +1804,16 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <v>-100</v>
@@ -1785,56 +1822,56 @@
         <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
-        <v>-100</v>
-      </c>
       <c r="K21" s="3">
         <v>-100</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R21" s="3">
         <v>-100</v>
       </c>
       <c r="S21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U21" s="3">
         <v>-100</v>
       </c>
       <c r="V21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
-        <v>-100</v>
-      </c>
       <c r="X21" s="3">
         <v>-100</v>
       </c>
@@ -1848,19 +1885,22 @@
         <v>-100</v>
       </c>
       <c r="AB21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-300</v>
       </c>
-      <c r="AD21" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,13 +1988,16 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <v>-100</v>
@@ -1963,31 +2006,31 @@
         <v>-100</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
-        <v>-100</v>
-      </c>
       <c r="K23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P23" s="3">
         <v>-100</v>
@@ -1999,46 +2042,49 @@
         <v>-100</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U23" s="3">
         <v>-100</v>
       </c>
       <c r="V23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
-        <v>-100</v>
-      </c>
       <c r="X23" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y23" s="3">
         <v>-200</v>
       </c>
       <c r="Z23" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA23" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB23" s="3">
         <v>-200</v>
       </c>
       <c r="AC23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AD23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,13 +2264,16 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <v>-100</v>
@@ -2230,31 +2282,31 @@
         <v>-100</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
-        <v>-100</v>
-      </c>
       <c r="K26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P26" s="3">
         <v>-100</v>
@@ -2266,51 +2318,54 @@
         <v>-100</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U26" s="3">
         <v>-100</v>
       </c>
       <c r="V26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
-        <v>-100</v>
-      </c>
       <c r="X26" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y26" s="3">
         <v>-200</v>
       </c>
       <c r="Z26" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA26" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB26" s="3">
         <v>-200</v>
       </c>
       <c r="AC26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AD26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <v>-100</v>
@@ -2319,31 +2374,31 @@
         <v>-100</v>
       </c>
       <c r="G27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
-        <v>-100</v>
-      </c>
       <c r="K27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P27" s="3">
         <v>-100</v>
@@ -2355,46 +2410,49 @@
         <v>-100</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U27" s="3">
         <v>-100</v>
       </c>
       <c r="V27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
-        <v>-100</v>
-      </c>
       <c r="X27" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y27" s="3">
         <v>-200</v>
       </c>
       <c r="Z27" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA27" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB27" s="3">
         <v>-200</v>
       </c>
       <c r="AC27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2764,14 +2834,14 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2785,10 +2855,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2803,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -2838,13 +2908,16 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <v>-100</v>
@@ -2853,31 +2926,31 @@
         <v>-100</v>
       </c>
       <c r="G33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
-        <v>-100</v>
-      </c>
       <c r="K33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P33" s="3">
         <v>-100</v>
@@ -2889,46 +2962,49 @@
         <v>-100</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U33" s="3">
         <v>-100</v>
       </c>
       <c r="V33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
-        <v>-100</v>
-      </c>
       <c r="X33" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y33" s="3">
         <v>-200</v>
       </c>
       <c r="Z33" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA33" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB33" s="3">
         <v>-200</v>
       </c>
       <c r="AC33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AD33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,13 +3092,16 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <v>-100</v>
@@ -3031,31 +3110,31 @@
         <v>-100</v>
       </c>
       <c r="G35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
-        <v>-100</v>
-      </c>
       <c r="K35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3">
         <v>-100</v>
@@ -3067,140 +3146,146 @@
         <v>-100</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3">
         <v>-100</v>
       </c>
       <c r="V35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
-        <v>-100</v>
-      </c>
       <c r="X35" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y35" s="3">
         <v>-200</v>
       </c>
       <c r="Z35" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA35" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB35" s="3">
         <v>-200</v>
       </c>
       <c r="AC35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AD35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3351,9 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3274,40 +3361,40 @@
         <v>200</v>
       </c>
       <c r="E41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F41" s="3">
+        <v>100</v>
+      </c>
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>200</v>
       </c>
       <c r="I41" s="3">
         <v>200</v>
       </c>
       <c r="J41" s="3">
+        <v>200</v>
+      </c>
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>300</v>
-      </c>
-      <c r="M41" s="3">
-        <v>200</v>
       </c>
       <c r="N41" s="3">
         <v>200</v>
       </c>
       <c r="O41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="3">
         <v>100</v>
@@ -3316,7 +3403,7 @@
         <v>100</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -3325,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W41" s="3">
         <v>100</v>
@@ -3337,25 +3424,28 @@
         <v>100</v>
       </c>
       <c r="Z41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA41" s="3">
         <v>200</v>
       </c>
       <c r="AB41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC41" s="3">
         <v>300</v>
       </c>
       <c r="AD41" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AE41" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3461,11 +3554,11 @@
         <v>0</v>
       </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
         <v>0</v>
       </c>
@@ -3527,18 +3620,21 @@
         <v>0</v>
       </c>
       <c r="AD43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E44" s="3">
         <v>600</v>
@@ -3547,22 +3643,22 @@
         <v>600</v>
       </c>
       <c r="G44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H44" s="3">
         <v>500</v>
       </c>
       <c r="I44" s="3">
+        <v>500</v>
+      </c>
+      <c r="J44" s="3">
         <v>600</v>
-      </c>
-      <c r="J44" s="3">
-        <v>500</v>
       </c>
       <c r="K44" s="3">
         <v>500</v>
       </c>
       <c r="L44" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M44" s="3">
         <v>600</v>
@@ -3586,7 +3682,7 @@
         <v>600</v>
       </c>
       <c r="T44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U44" s="3">
         <v>700</v>
@@ -3595,10 +3691,10 @@
         <v>700</v>
       </c>
       <c r="W44" s="3">
+        <v>700</v>
+      </c>
+      <c r="X44" s="3">
         <v>1400</v>
-      </c>
-      <c r="X44" s="3">
-        <v>800</v>
       </c>
       <c r="Y44" s="3">
         <v>800</v>
@@ -3607,22 +3703,25 @@
         <v>800</v>
       </c>
       <c r="AA44" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB44" s="3">
         <v>700</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>800</v>
       </c>
       <c r="AC44" s="3">
         <v>800</v>
       </c>
       <c r="AD44" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AE44" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3635,8 +3734,8 @@
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -3660,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
@@ -3699,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="AB45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -3710,8 +3809,11 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3719,40 +3821,40 @@
         <v>800</v>
       </c>
       <c r="E46" s="3">
+        <v>800</v>
+      </c>
+      <c r="F46" s="3">
         <v>700</v>
-      </c>
-      <c r="F46" s="3">
-        <v>800</v>
       </c>
       <c r="G46" s="3">
         <v>800</v>
       </c>
       <c r="H46" s="3">
+        <v>800</v>
+      </c>
+      <c r="I46" s="3">
         <v>1000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
-      </c>
-      <c r="M46" s="3">
-        <v>800</v>
       </c>
       <c r="N46" s="3">
         <v>800</v>
       </c>
       <c r="O46" s="3">
+        <v>800</v>
+      </c>
+      <c r="P46" s="3">
         <v>700</v>
-      </c>
-      <c r="P46" s="3">
-        <v>800</v>
       </c>
       <c r="Q46" s="3">
         <v>800</v>
@@ -3770,19 +3872,19 @@
         <v>800</v>
       </c>
       <c r="V46" s="3">
+        <v>800</v>
+      </c>
+      <c r="W46" s="3">
         <v>900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>1100</v>
       </c>
       <c r="AA46" s="3">
         <v>1100</v>
@@ -3791,16 +3893,19 @@
         <v>1100</v>
       </c>
       <c r="AC46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD46" s="3">
         <v>1200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3918,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3">
         <v>100</v>
@@ -3927,16 +4035,16 @@
         <v>100</v>
       </c>
       <c r="O48" s="3">
+        <v>100</v>
+      </c>
+      <c r="P48" s="3">
         <v>200</v>
       </c>
-      <c r="P48" s="3">
-        <v>100</v>
-      </c>
       <c r="Q48" s="3">
         <v>100</v>
       </c>
       <c r="R48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S48" s="3">
         <v>200</v>
@@ -3948,19 +4056,19 @@
         <v>200</v>
       </c>
       <c r="V48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W48" s="3">
+        <v>100</v>
+      </c>
+      <c r="X48" s="3">
         <v>200</v>
       </c>
-      <c r="X48" s="3">
-        <v>100</v>
-      </c>
       <c r="Y48" s="3">
         <v>100</v>
       </c>
       <c r="Z48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA48" s="3">
         <v>200</v>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4256,16 +4376,16 @@
         <v>700</v>
       </c>
       <c r="F52" s="3">
+        <v>700</v>
+      </c>
+      <c r="G52" s="3">
         <v>600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>700</v>
       </c>
       <c r="H52" s="3">
         <v>700</v>
       </c>
       <c r="I52" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J52" s="3">
         <v>600</v>
@@ -4274,7 +4394,7 @@
         <v>600</v>
       </c>
       <c r="L52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M52" s="3">
         <v>700</v>
@@ -4283,7 +4403,7 @@
         <v>700</v>
       </c>
       <c r="O52" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="P52" s="3">
         <v>600</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4545,11 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4431,28 +4557,28 @@
         <v>1500</v>
       </c>
       <c r="E54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F54" s="3">
         <v>1400</v>
-      </c>
-      <c r="F54" s="3">
-        <v>1500</v>
       </c>
       <c r="G54" s="3">
         <v>1500</v>
       </c>
       <c r="H54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I54" s="3">
         <v>1600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>1500</v>
       </c>
       <c r="J54" s="3">
         <v>1500</v>
       </c>
       <c r="K54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L54" s="3">
         <v>1700</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1600</v>
       </c>
       <c r="M54" s="3">
         <v>1600</v>
@@ -4461,10 +4587,10 @@
         <v>1600</v>
       </c>
       <c r="O54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P54" s="3">
         <v>1400</v>
-      </c>
-      <c r="P54" s="3">
-        <v>1600</v>
       </c>
       <c r="Q54" s="3">
         <v>1600</v>
@@ -4485,34 +4611,37 @@
         <v>1600</v>
       </c>
       <c r="W54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X54" s="3">
         <v>1800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,16 +4707,17 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>200</v>
@@ -4595,13 +4726,13 @@
         <v>200</v>
       </c>
       <c r="H57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>300</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
@@ -4616,10 +4747,10 @@
         <v>200</v>
       </c>
       <c r="O57" s="3">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>400</v>
       </c>
       <c r="Q57" s="3">
         <v>400</v>
@@ -4628,19 +4759,19 @@
         <v>400</v>
       </c>
       <c r="S57" s="3">
+        <v>400</v>
+      </c>
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
-      </c>
-      <c r="U57" s="3">
-        <v>300</v>
       </c>
       <c r="V57" s="3">
         <v>300</v>
       </c>
       <c r="W57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X57" s="3">
         <v>200</v>
@@ -4652,22 +4783,25 @@
         <v>200</v>
       </c>
       <c r="AA57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
       </c>
       <c r="AD57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4687,7 +4821,7 @@
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
@@ -4696,25 +4830,25 @@
         <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
         <v>400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>300</v>
       </c>
       <c r="N58" s="3">
         <v>300</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>200</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S58" s="3">
         <v>100</v>
@@ -4726,7 +4860,7 @@
         <v>100</v>
       </c>
       <c r="V58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
         <v>200</v>
@@ -4735,7 +4869,7 @@
         <v>200</v>
       </c>
       <c r="Y58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z58" s="3">
         <v>100</v>
@@ -4755,13 +4889,16 @@
       <c r="AE58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
         <v>100</v>
@@ -4815,10 +4952,10 @@
         <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X59" s="3">
         <v>100</v>
@@ -4844,8 +4981,11 @@
       <c r="AE59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4856,13 +4996,13 @@
         <v>400</v>
       </c>
       <c r="F60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G60" s="3">
         <v>300</v>
       </c>
       <c r="H60" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I60" s="3">
         <v>500</v>
@@ -4874,7 +5014,7 @@
         <v>500</v>
       </c>
       <c r="L60" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M60" s="3">
         <v>600</v>
@@ -4883,10 +5023,10 @@
         <v>600</v>
       </c>
       <c r="O60" s="3">
+        <v>600</v>
+      </c>
+      <c r="P60" s="3">
         <v>500</v>
-      </c>
-      <c r="P60" s="3">
-        <v>600</v>
       </c>
       <c r="Q60" s="3">
         <v>600</v>
@@ -4895,34 +5035,34 @@
         <v>600</v>
       </c>
       <c r="S60" s="3">
+        <v>600</v>
+      </c>
+      <c r="T60" s="3">
         <v>400</v>
-      </c>
-      <c r="T60" s="3">
-        <v>600</v>
       </c>
       <c r="U60" s="3">
         <v>600</v>
       </c>
       <c r="V60" s="3">
+        <v>600</v>
+      </c>
+      <c r="W60" s="3">
         <v>500</v>
-      </c>
-      <c r="W60" s="3">
-        <v>400</v>
       </c>
       <c r="X60" s="3">
         <v>400</v>
       </c>
       <c r="Y60" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z60" s="3">
         <v>300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>300</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>400</v>
       </c>
       <c r="AC60" s="3">
         <v>400</v>
@@ -4933,8 +5073,11 @@
       <c r="AE60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4942,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -4960,11 +5103,11 @@
         <v>100</v>
       </c>
       <c r="K61" s="3">
+        <v>100</v>
+      </c>
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
-        <v>100</v>
-      </c>
       <c r="M61" s="3">
         <v>100</v>
       </c>
@@ -5011,7 +5154,7 @@
         <v>100</v>
       </c>
       <c r="AB61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC61" s="3">
         <v>200</v>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5067,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -5081,14 +5227,14 @@
       <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3" t="s">
+      <c r="V62" s="3">
+        <v>100</v>
+      </c>
+      <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W62" s="3">
-        <v>100</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
+      <c r="X62" s="3">
+        <v>100</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
@@ -5096,8 +5242,8 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,73 +5533,76 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>400</v>
+      </c>
+      <c r="E66" s="3">
         <v>500</v>
-      </c>
-      <c r="E66" s="3">
-        <v>400</v>
       </c>
       <c r="F66" s="3">
         <v>400</v>
       </c>
       <c r="G66" s="3">
+        <v>400</v>
+      </c>
+      <c r="H66" s="3">
         <v>500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>700</v>
       </c>
       <c r="J66" s="3">
         <v>700</v>
       </c>
       <c r="K66" s="3">
+        <v>700</v>
+      </c>
+      <c r="L66" s="3">
         <v>800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>700</v>
       </c>
       <c r="M66" s="3">
         <v>700</v>
       </c>
       <c r="N66" s="3">
+        <v>700</v>
+      </c>
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>800</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>700</v>
       </c>
       <c r="R66" s="3">
         <v>700</v>
       </c>
       <c r="S66" s="3">
+        <v>700</v>
+      </c>
+      <c r="T66" s="3">
         <v>600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
-      </c>
-      <c r="V66" s="3">
-        <v>600</v>
       </c>
       <c r="W66" s="3">
         <v>600</v>
       </c>
       <c r="X66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Y66" s="3">
         <v>500</v>
@@ -5459,7 +5617,7 @@
         <v>500</v>
       </c>
       <c r="AC66" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AD66" s="3">
         <v>600</v>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,8 +6027,11 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5865,34 +6039,34 @@
         <v>-10600</v>
       </c>
       <c r="E72" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-10500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10400</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-10300</v>
       </c>
       <c r="H72" s="3">
         <v>-10300</v>
       </c>
       <c r="I72" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="J72" s="3">
         <v>-10500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10100</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-9900</v>
       </c>
       <c r="M72" s="3">
         <v>-9900</v>
       </c>
       <c r="N72" s="3">
-        <v>-9800</v>
+        <v>-9900</v>
       </c>
       <c r="O72" s="3">
         <v>-9800</v>
@@ -5901,52 +6075,55 @@
         <v>-9800</v>
       </c>
       <c r="Q72" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="R72" s="3">
         <v>-9700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-9600</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-9400</v>
       </c>
       <c r="T72" s="3">
         <v>-9400</v>
       </c>
       <c r="U72" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="V72" s="3">
         <v>-9300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-9200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,8 +6395,11 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6221,22 +6407,22 @@
         <v>1100</v>
       </c>
       <c r="E76" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F76" s="3">
         <v>900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1000</v>
       </c>
       <c r="H76" s="3">
         <v>1000</v>
       </c>
       <c r="I76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J76" s="3">
         <v>800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>900</v>
       </c>
       <c r="K76" s="3">
         <v>900</v>
@@ -6245,7 +6431,7 @@
         <v>900</v>
       </c>
       <c r="M76" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N76" s="3">
         <v>800</v>
@@ -6263,28 +6449,28 @@
         <v>800</v>
       </c>
       <c r="S76" s="3">
+        <v>800</v>
+      </c>
+      <c r="T76" s="3">
         <v>1000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1000</v>
-      </c>
-      <c r="W76" s="3">
-        <v>1200</v>
       </c>
       <c r="X76" s="3">
         <v>1200</v>
       </c>
       <c r="Y76" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z76" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>1400</v>
       </c>
       <c r="AA76" s="3">
         <v>1400</v>
@@ -6293,16 +6479,19 @@
         <v>1400</v>
       </c>
       <c r="AC76" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD76" s="3">
         <v>1500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,107 +6579,113 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
         <v>-100</v>
@@ -6499,31 +6694,31 @@
         <v>-100</v>
       </c>
       <c r="G81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
-        <v>-100</v>
-      </c>
       <c r="K81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P81" s="3">
         <v>-100</v>
@@ -6535,46 +6730,49 @@
         <v>-100</v>
       </c>
       <c r="S81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U81" s="3">
         <v>-100</v>
       </c>
       <c r="V81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
-        <v>-100</v>
-      </c>
       <c r="X81" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y81" s="3">
         <v>-200</v>
       </c>
       <c r="Z81" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA81" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB81" s="3">
         <v>-200</v>
       </c>
       <c r="AC81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AD81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,35 +7354,38 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
@@ -7185,22 +7402,22 @@
         <v>0</v>
       </c>
       <c r="Q89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
       <c r="V89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W89" s="3">
         <v>-100</v>
@@ -7215,22 +7432,25 @@
         <v>-100</v>
       </c>
       <c r="AA89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AB89" s="3">
-        <v>-100</v>
-      </c>
       <c r="AC89" s="3">
         <v>-100</v>
       </c>
       <c r="AD89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,16 +7756,19 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8016,7 +8262,7 @@
         <v>100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
@@ -8025,34 +8271,34 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
-        <v>100</v>
-      </c>
       <c r="M100" s="3">
         <v>100</v>
       </c>
       <c r="N100" s="3">
+        <v>100</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R100" s="3">
         <v>100</v>
@@ -8061,7 +8307,7 @@
         <v>100</v>
       </c>
       <c r="T100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -8070,13 +8316,13 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="3">
         <v>100</v>
@@ -8085,7 +8331,7 @@
         <v>100</v>
       </c>
       <c r="AB100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -8094,10 +8340,13 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,8 +8434,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8194,40 +8446,40 @@
         <v>100</v>
       </c>
       <c r="E102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>-100</v>
       </c>
       <c r="G102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I102" s="3">
         <v>-100</v>
       </c>
       <c r="J102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
-        <v>100</v>
-      </c>
       <c r="M102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
-        <v>-100</v>
-      </c>
       <c r="P102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
@@ -8254,24 +8506,27 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB102" s="3">
         <v>-100</v>
       </c>
       <c r="AC102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IVDN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IVDN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>IVDN</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -800,31 +804,31 @@
         <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -833,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -851,48 +855,51 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <v>100</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
       <c r="AA8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <v>100</v>
       </c>
       <c r="AC8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <v>200</v>
       </c>
       <c r="AF8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -901,10 +908,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -913,19 +920,19 @@
         <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
@@ -943,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3">
         <v>100</v>
@@ -952,33 +959,36 @@
         <v>100</v>
       </c>
       <c r="Z9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
         <v>100</v>
       </c>
       <c r="AC9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3">
         <v>100</v>
       </c>
       <c r="AF9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -987,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -999,10 +1009,10 @@
         <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
@@ -1014,13 +1024,13 @@
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
@@ -1041,10 +1051,10 @@
         <v>0</v>
       </c>
       <c r="Y10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA10" s="3">
         <v>0</v>
@@ -1056,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3">
         <v>100</v>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1311,11 +1331,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
@@ -1326,8 +1346,8 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1335,20 +1355,20 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
@@ -1359,8 +1379,8 @@
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1374,19 +1394,22 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
+      <c r="F15" s="3">
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>4</v>
@@ -1403,8 +1426,8 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,38 +1523,39 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3">
         <v>200</v>
       </c>
       <c r="F17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G17" s="3">
         <v>100</v>
       </c>
       <c r="H17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I17" s="3">
         <v>200</v>
       </c>
       <c r="J17" s="3">
+        <v>200</v>
+      </c>
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="L17" s="3">
-        <v>100</v>
-      </c>
       <c r="M17" s="3">
         <v>100</v>
       </c>
@@ -1551,19 +1578,19 @@
         <v>100</v>
       </c>
       <c r="T17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U17" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V17" s="3">
         <v>200</v>
       </c>
       <c r="W17" s="3">
+        <v>200</v>
+      </c>
+      <c r="X17" s="3">
         <v>400</v>
-      </c>
-      <c r="X17" s="3">
-        <v>200</v>
       </c>
       <c r="Y17" s="3">
         <v>200</v>
@@ -1572,30 +1599,33 @@
         <v>200</v>
       </c>
       <c r="AA17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB17" s="3">
         <v>300</v>
       </c>
       <c r="AC17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD17" s="3">
         <v>200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>500</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>300</v>
       </c>
       <c r="AF17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3">
         <v>-100</v>
@@ -1604,28 +1634,28 @@
         <v>-100</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
-        <v>-100</v>
-      </c>
       <c r="J18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
-        <v>-100</v>
-      </c>
       <c r="L18" s="3">
         <v>-100</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
@@ -1634,31 +1664,31 @@
         <v>-100</v>
       </c>
       <c r="Q18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
         <v>-100</v>
       </c>
       <c r="T18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
         <v>-200</v>
       </c>
       <c r="W18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X18" s="3">
         <v>-300</v>
       </c>
-      <c r="X18" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z18" s="3">
         <v>-200</v>
@@ -1673,16 +1703,19 @@
         <v>-200</v>
       </c>
       <c r="AD18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AE18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1733,14 +1767,14 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1754,10 +1788,10 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1772,10 +1806,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1807,16 +1841,19 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>-100</v>
@@ -1825,56 +1862,56 @@
         <v>-100</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
-        <v>-100</v>
-      </c>
       <c r="L21" s="3">
         <v>-100</v>
       </c>
       <c r="M21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
         <v>-100</v>
       </c>
       <c r="T21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3">
         <v>-100</v>
       </c>
       <c r="W21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X21" s="3">
         <v>-200</v>
       </c>
-      <c r="X21" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y21" s="3">
         <v>-100</v>
       </c>
@@ -1888,19 +1925,22 @@
         <v>-100</v>
       </c>
       <c r="AC21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-300</v>
       </c>
-      <c r="AE21" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,16 +2031,19 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>-100</v>
@@ -2009,31 +2052,31 @@
         <v>-100</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
-        <v>-100</v>
-      </c>
       <c r="L23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="3">
         <v>-100</v>
@@ -2045,46 +2088,49 @@
         <v>-100</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
         <v>-100</v>
       </c>
       <c r="W23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y23" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z23" s="3">
         <v>-200</v>
       </c>
       <c r="AA23" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB23" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC23" s="3">
         <v>-200</v>
       </c>
       <c r="AD23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,16 +2316,19 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
         <v>-100</v>
@@ -2285,31 +2337,31 @@
         <v>-100</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
-        <v>-100</v>
-      </c>
       <c r="L26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3">
         <v>-100</v>
@@ -2321,54 +2373,57 @@
         <v>-100</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
         <v>-100</v>
       </c>
       <c r="W26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y26" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z26" s="3">
         <v>-200</v>
       </c>
       <c r="AA26" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB26" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC26" s="3">
         <v>-200</v>
       </c>
       <c r="AD26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AE26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
         <v>-100</v>
@@ -2377,31 +2432,31 @@
         <v>-100</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
-        <v>-100</v>
-      </c>
       <c r="L27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3">
         <v>-100</v>
@@ -2413,46 +2468,49 @@
         <v>-100</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
         <v>-100</v>
       </c>
       <c r="W27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y27" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z27" s="3">
         <v>-200</v>
       </c>
       <c r="AA27" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB27" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC27" s="3">
         <v>-200</v>
       </c>
       <c r="AD27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2837,14 +2907,14 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2858,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2876,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -2911,16 +2981,19 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
         <v>-100</v>
@@ -2929,31 +3002,31 @@
         <v>-100</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
-        <v>-100</v>
-      </c>
       <c r="L33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3">
         <v>-100</v>
@@ -2965,46 +3038,49 @@
         <v>-100</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
         <v>-100</v>
       </c>
       <c r="W33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y33" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z33" s="3">
         <v>-200</v>
       </c>
       <c r="AA33" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB33" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC33" s="3">
         <v>-200</v>
       </c>
       <c r="AD33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
-      <c r="AE33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,16 +3171,19 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
         <v>-100</v>
@@ -3113,31 +3192,31 @@
         <v>-100</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
-        <v>-100</v>
-      </c>
       <c r="L35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3">
         <v>-100</v>
@@ -3149,143 +3228,149 @@
         <v>-100</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
         <v>-100</v>
       </c>
       <c r="W35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y35" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z35" s="3">
         <v>-200</v>
       </c>
       <c r="AA35" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB35" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC35" s="3">
         <v>-200</v>
       </c>
       <c r="AD35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
-      <c r="AE35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3438,9 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3364,40 +3451,40 @@
         <v>200</v>
       </c>
       <c r="F41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G41" s="3">
+        <v>100</v>
+      </c>
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>200</v>
       </c>
       <c r="J41" s="3">
         <v>200</v>
       </c>
       <c r="K41" s="3">
+        <v>200</v>
+      </c>
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>300</v>
-      </c>
-      <c r="N41" s="3">
-        <v>200</v>
       </c>
       <c r="O41" s="3">
         <v>200</v>
       </c>
       <c r="P41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R41" s="3">
         <v>100</v>
@@ -3406,7 +3493,7 @@
         <v>100</v>
       </c>
       <c r="T41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U41" s="3">
         <v>0</v>
@@ -3415,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="W41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X41" s="3">
         <v>100</v>
@@ -3427,25 +3514,28 @@
         <v>100</v>
       </c>
       <c r="AA41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB41" s="3">
         <v>200</v>
       </c>
       <c r="AC41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD41" s="3">
         <v>300</v>
       </c>
       <c r="AE41" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AF41" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3626,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3557,11 +3650,11 @@
         <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
@@ -3623,21 +3716,24 @@
         <v>0</v>
       </c>
       <c r="AE43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>600</v>
+      </c>
+      <c r="E44" s="3">
         <v>500</v>
-      </c>
-      <c r="E44" s="3">
-        <v>600</v>
       </c>
       <c r="F44" s="3">
         <v>600</v>
@@ -3646,22 +3742,22 @@
         <v>600</v>
       </c>
       <c r="H44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I44" s="3">
         <v>500</v>
       </c>
       <c r="J44" s="3">
+        <v>500</v>
+      </c>
+      <c r="K44" s="3">
         <v>600</v>
-      </c>
-      <c r="K44" s="3">
-        <v>500</v>
       </c>
       <c r="L44" s="3">
         <v>500</v>
       </c>
       <c r="M44" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N44" s="3">
         <v>600</v>
@@ -3685,7 +3781,7 @@
         <v>600</v>
       </c>
       <c r="U44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V44" s="3">
         <v>700</v>
@@ -3694,10 +3790,10 @@
         <v>700</v>
       </c>
       <c r="X44" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y44" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>800</v>
       </c>
       <c r="Z44" s="3">
         <v>800</v>
@@ -3706,27 +3802,30 @@
         <v>800</v>
       </c>
       <c r="AB44" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC44" s="3">
         <v>700</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>800</v>
       </c>
       <c r="AD44" s="3">
         <v>800</v>
       </c>
       <c r="AE44" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AF44" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -3737,8 +3836,8 @@
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
@@ -3762,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -3801,7 +3900,7 @@
         <v>100</v>
       </c>
       <c r="AC45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -3812,8 +3911,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3824,40 +3926,40 @@
         <v>800</v>
       </c>
       <c r="F46" s="3">
+        <v>800</v>
+      </c>
+      <c r="G46" s="3">
         <v>700</v>
-      </c>
-      <c r="G46" s="3">
-        <v>800</v>
       </c>
       <c r="H46" s="3">
         <v>800</v>
       </c>
       <c r="I46" s="3">
+        <v>800</v>
+      </c>
+      <c r="J46" s="3">
         <v>1000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
-      </c>
-      <c r="N46" s="3">
-        <v>800</v>
       </c>
       <c r="O46" s="3">
         <v>800</v>
       </c>
       <c r="P46" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q46" s="3">
         <v>700</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>800</v>
       </c>
       <c r="R46" s="3">
         <v>800</v>
@@ -3875,19 +3977,19 @@
         <v>800</v>
       </c>
       <c r="W46" s="3">
+        <v>800</v>
+      </c>
+      <c r="X46" s="3">
         <v>900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>1100</v>
       </c>
       <c r="AB46" s="3">
         <v>1100</v>
@@ -3896,16 +3998,19 @@
         <v>1100</v>
       </c>
       <c r="AD46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE46" s="3">
         <v>1200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,8 +4101,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4029,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
@@ -4038,16 +4146,16 @@
         <v>100</v>
       </c>
       <c r="P48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3">
-        <v>100</v>
-      </c>
       <c r="R48" s="3">
         <v>100</v>
       </c>
       <c r="S48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T48" s="3">
         <v>200</v>
@@ -4059,19 +4167,19 @@
         <v>200</v>
       </c>
       <c r="W48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y48" s="3">
         <v>200</v>
       </c>
-      <c r="Y48" s="3">
-        <v>100</v>
-      </c>
       <c r="Z48" s="3">
         <v>100</v>
       </c>
       <c r="AA48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB48" s="3">
         <v>200</v>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4379,16 +4499,16 @@
         <v>700</v>
       </c>
       <c r="G52" s="3">
+        <v>700</v>
+      </c>
+      <c r="H52" s="3">
         <v>600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>700</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
       </c>
       <c r="J52" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K52" s="3">
         <v>600</v>
@@ -4397,7 +4517,7 @@
         <v>600</v>
       </c>
       <c r="M52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N52" s="3">
         <v>700</v>
@@ -4406,7 +4526,7 @@
         <v>700</v>
       </c>
       <c r="P52" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q52" s="3">
         <v>600</v>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,8 +4671,11 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4560,28 +4686,28 @@
         <v>1500</v>
       </c>
       <c r="F54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G54" s="3">
         <v>1400</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1500</v>
       </c>
       <c r="H54" s="3">
         <v>1500</v>
       </c>
       <c r="I54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J54" s="3">
         <v>1600</v>
-      </c>
-      <c r="J54" s="3">
-        <v>1500</v>
       </c>
       <c r="K54" s="3">
         <v>1500</v>
       </c>
       <c r="L54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M54" s="3">
         <v>1700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>1600</v>
       </c>
       <c r="N54" s="3">
         <v>1600</v>
@@ -4590,10 +4716,10 @@
         <v>1600</v>
       </c>
       <c r="P54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q54" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>1600</v>
       </c>
       <c r="R54" s="3">
         <v>1600</v>
@@ -4614,34 +4740,37 @@
         <v>1600</v>
       </c>
       <c r="X54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Y54" s="3">
         <v>1800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,19 +4838,20 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
@@ -4729,13 +4860,13 @@
         <v>200</v>
       </c>
       <c r="I57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>300</v>
       </c>
       <c r="K57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
@@ -4750,10 +4881,10 @@
         <v>200</v>
       </c>
       <c r="P57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>400</v>
       </c>
       <c r="R57" s="3">
         <v>400</v>
@@ -4762,19 +4893,19 @@
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
-      </c>
-      <c r="V57" s="3">
-        <v>300</v>
       </c>
       <c r="W57" s="3">
         <v>300</v>
       </c>
       <c r="X57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y57" s="3">
         <v>200</v>
@@ -4786,22 +4917,25 @@
         <v>200</v>
       </c>
       <c r="AB57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD57" s="3">
         <v>200</v>
       </c>
       <c r="AE57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4824,7 +4958,7 @@
         <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
@@ -4833,25 +4967,25 @@
         <v>200</v>
       </c>
       <c r="M58" s="3">
+        <v>200</v>
+      </c>
+      <c r="N58" s="3">
         <v>400</v>
-      </c>
-      <c r="N58" s="3">
-        <v>300</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>200</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T58" s="3">
         <v>100</v>
@@ -4863,7 +4997,7 @@
         <v>100</v>
       </c>
       <c r="W58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X58" s="3">
         <v>200</v>
@@ -4872,7 +5006,7 @@
         <v>200</v>
       </c>
       <c r="Z58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA58" s="3">
         <v>100</v>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4901,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -4955,10 +5092,10 @@
         <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="3">
         <v>100</v>
@@ -4984,13 +5121,16 @@
       <c r="AF59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
         <v>400</v>
@@ -4999,13 +5139,13 @@
         <v>400</v>
       </c>
       <c r="G60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H60" s="3">
         <v>300</v>
       </c>
       <c r="I60" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J60" s="3">
         <v>500</v>
@@ -5017,7 +5157,7 @@
         <v>500</v>
       </c>
       <c r="M60" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N60" s="3">
         <v>600</v>
@@ -5026,10 +5166,10 @@
         <v>600</v>
       </c>
       <c r="P60" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q60" s="3">
         <v>500</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>600</v>
       </c>
       <c r="R60" s="3">
         <v>600</v>
@@ -5038,34 +5178,34 @@
         <v>600</v>
       </c>
       <c r="T60" s="3">
+        <v>600</v>
+      </c>
+      <c r="U60" s="3">
         <v>400</v>
-      </c>
-      <c r="U60" s="3">
-        <v>600</v>
       </c>
       <c r="V60" s="3">
         <v>600</v>
       </c>
       <c r="W60" s="3">
+        <v>600</v>
+      </c>
+      <c r="X60" s="3">
         <v>500</v>
-      </c>
-      <c r="X60" s="3">
-        <v>400</v>
       </c>
       <c r="Y60" s="3">
         <v>400</v>
       </c>
       <c r="Z60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA60" s="3">
         <v>300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>300</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>400</v>
       </c>
       <c r="AD60" s="3">
         <v>400</v>
@@ -5076,8 +5216,11 @@
       <c r="AF60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5088,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
@@ -5106,11 +5249,11 @@
         <v>100</v>
       </c>
       <c r="L61" s="3">
+        <v>100</v>
+      </c>
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
-        <v>100</v>
-      </c>
       <c r="N61" s="3">
         <v>100</v>
       </c>
@@ -5157,7 +5300,7 @@
         <v>100</v>
       </c>
       <c r="AC61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD61" s="3">
         <v>200</v>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5216,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -5230,14 +5376,14 @@
       <c r="V62" s="3">
         <v>100</v>
       </c>
-      <c r="W62" s="3" t="s">
+      <c r="W62" s="3">
+        <v>100</v>
+      </c>
+      <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
+      <c r="Y62" s="3">
+        <v>100</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
@@ -5245,8 +5391,8 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,76 +5691,79 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200</v>
+      </c>
+      <c r="E66" s="3">
         <v>400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>500</v>
-      </c>
-      <c r="F66" s="3">
-        <v>400</v>
       </c>
       <c r="G66" s="3">
         <v>400</v>
       </c>
       <c r="H66" s="3">
+        <v>400</v>
+      </c>
+      <c r="I66" s="3">
         <v>500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>700</v>
       </c>
       <c r="K66" s="3">
         <v>700</v>
       </c>
       <c r="L66" s="3">
+        <v>700</v>
+      </c>
+      <c r="M66" s="3">
         <v>800</v>
-      </c>
-      <c r="M66" s="3">
-        <v>700</v>
       </c>
       <c r="N66" s="3">
         <v>700</v>
       </c>
       <c r="O66" s="3">
+        <v>700</v>
+      </c>
+      <c r="P66" s="3">
         <v>800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>800</v>
-      </c>
-      <c r="R66" s="3">
-        <v>700</v>
       </c>
       <c r="S66" s="3">
         <v>700</v>
       </c>
       <c r="T66" s="3">
+        <v>700</v>
+      </c>
+      <c r="U66" s="3">
         <v>600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
-      </c>
-      <c r="W66" s="3">
-        <v>600</v>
       </c>
       <c r="X66" s="3">
         <v>600</v>
       </c>
       <c r="Y66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Z66" s="3">
         <v>500</v>
@@ -5620,7 +5778,7 @@
         <v>500</v>
       </c>
       <c r="AD66" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AE66" s="3">
         <v>600</v>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,46 +6201,49 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-10600</v>
+        <v>-10700</v>
       </c>
       <c r="E72" s="3">
         <v>-10600</v>
       </c>
       <c r="F72" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="G72" s="3">
         <v>-10500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10400</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-10300</v>
       </c>
       <c r="I72" s="3">
         <v>-10300</v>
       </c>
       <c r="J72" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-10500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10100</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-9900</v>
       </c>
       <c r="N72" s="3">
         <v>-9900</v>
       </c>
       <c r="O72" s="3">
-        <v>-9800</v>
+        <v>-9900</v>
       </c>
       <c r="P72" s="3">
         <v>-9800</v>
@@ -6078,52 +6252,55 @@
         <v>-9800</v>
       </c>
       <c r="R72" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="S72" s="3">
         <v>-9700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9600</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-9400</v>
       </c>
       <c r="U72" s="3">
         <v>-9400</v>
       </c>
       <c r="V72" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="W72" s="3">
         <v>-9300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-9200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-8300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,34 +6581,37 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="E76" s="3">
         <v>1100</v>
       </c>
       <c r="F76" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G76" s="3">
         <v>900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1100</v>
-      </c>
-      <c r="H76" s="3">
-        <v>1000</v>
       </c>
       <c r="I76" s="3">
         <v>1000</v>
       </c>
       <c r="J76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K76" s="3">
         <v>800</v>
-      </c>
-      <c r="K76" s="3">
-        <v>900</v>
       </c>
       <c r="L76" s="3">
         <v>900</v>
@@ -6434,7 +6620,7 @@
         <v>900</v>
       </c>
       <c r="N76" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="O76" s="3">
         <v>800</v>
@@ -6452,28 +6638,28 @@
         <v>800</v>
       </c>
       <c r="T76" s="3">
+        <v>800</v>
+      </c>
+      <c r="U76" s="3">
         <v>1000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1000</v>
-      </c>
-      <c r="X76" s="3">
-        <v>1200</v>
       </c>
       <c r="Y76" s="3">
         <v>1200</v>
       </c>
       <c r="Z76" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA76" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>1400</v>
       </c>
       <c r="AB76" s="3">
         <v>1400</v>
@@ -6482,16 +6668,19 @@
         <v>1400</v>
       </c>
       <c r="AD76" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE76" s="3">
         <v>1500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,113 +6771,119 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F81" s="3">
         <v>-100</v>
@@ -6697,31 +6892,31 @@
         <v>-100</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
-        <v>-100</v>
-      </c>
       <c r="L81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="3">
         <v>-100</v>
@@ -6733,46 +6928,49 @@
         <v>-100</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V81" s="3">
         <v>-100</v>
       </c>
       <c r="W81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y81" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z81" s="3">
         <v>-200</v>
       </c>
       <c r="AA81" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB81" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC81" s="3">
         <v>-200</v>
       </c>
       <c r="AD81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
-      <c r="AE81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7571,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7366,29 +7583,29 @@
         <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
@@ -7405,22 +7622,22 @@
         <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
       <c r="W89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X89" s="3">
         <v>-100</v>
@@ -7435,22 +7652,25 @@
         <v>-100</v>
       </c>
       <c r="AB89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3">
-        <v>-100</v>
-      </c>
       <c r="AD89" s="3">
         <v>-100</v>
       </c>
       <c r="AE89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,19 +7986,22 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8496,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8265,7 +8511,7 @@
         <v>100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -8274,34 +8520,34 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
-        <v>100</v>
-      </c>
       <c r="N100" s="3">
         <v>100</v>
       </c>
       <c r="O100" s="3">
+        <v>100</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
         <v>100</v>
@@ -8310,7 +8556,7 @@
         <v>100</v>
       </c>
       <c r="U100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -8319,13 +8565,13 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA100" s="3">
         <v>100</v>
@@ -8334,7 +8580,7 @@
         <v>100</v>
       </c>
       <c r="AC100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -8343,10 +8589,13 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,52 +8686,55 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
         <v>100</v>
       </c>
       <c r="F102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G102" s="3">
         <v>-100</v>
       </c>
       <c r="H102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="J102" s="3">
         <v>-100</v>
       </c>
       <c r="K102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
-        <v>100</v>
-      </c>
       <c r="N102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
-        <v>-100</v>
-      </c>
       <c r="Q102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -8509,24 +8761,27 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC102" s="3">
         <v>-100</v>
       </c>
       <c r="AD102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-300</v>
       </c>
     </row>
